--- a/output/pdf_financials_xlsx/BZ.xlsx
+++ b/output/pdf_financials_xlsx/BZ.xlsx
@@ -999,43 +999,43 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000982</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00188</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00052</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>4.7e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000143</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.004272</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008907</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.005505</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.02284</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.023833</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.119018</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.143182</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.068693</v>
       </c>
     </row>
     <row r="13">
@@ -1879,43 +1879,43 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.192979</v>
+        <v>-0.193961</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.355824</v>
+        <v>-0.357704</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.734955</v>
+        <v>-0.735475</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.900763</v>
+        <v>-2.90081</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.437085</v>
+        <v>-0.437228</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.370932</v>
+        <v>-2.375204</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.641693</v>
+        <v>-0.6506</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.30385</v>
+        <v>-1.309355</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-9.459118999999999</v>
+        <v>-9.481959</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-12.636747</v>
+        <v>-12.66058</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-4.776962</v>
+        <v>-4.89598</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.024481</v>
+        <v>-4.167663</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-7.504189</v>
+        <v>-7.572882</v>
       </c>
     </row>
     <row r="28">
@@ -1989,43 +1989,43 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.192979</v>
+        <v>-0.193961</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.355824</v>
+        <v>-0.357704</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.734955</v>
+        <v>-0.735475</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.900763</v>
+        <v>-2.90081</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.437085</v>
+        <v>-0.437228</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.370932</v>
+        <v>-2.375204</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.641693</v>
+        <v>-0.6506</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.30385</v>
+        <v>-1.309355</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-9.459118999999999</v>
+        <v>-9.481959</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-12.636747</v>
+        <v>-12.66058</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.776962</v>
+        <v>-4.89598</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.024481</v>
+        <v>-4.167663</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-7.504189</v>
+        <v>-7.572882</v>
       </c>
     </row>
     <row r="30">
@@ -28702,7 +28702,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -32563,7 +32563,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -33623,7 +33623,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -35245,7 +35245,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -35605,7 +35605,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -37898,7 +37898,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">

--- a/output/pdf_financials_xlsx/BZ.xlsx
+++ b/output/pdf_financials_xlsx/BZ.xlsx
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.000431</v>
       </c>
     </row>
     <row r="29">
@@ -2025,7 +2025,7 @@
         <v>-4.167663</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-7.572882</v>
+        <v>-7.572451</v>
       </c>
     </row>
     <row r="30">
@@ -5977,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.009436</v>
       </c>
     </row>
     <row r="101">
@@ -15637,7 +15637,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -28164,7 +28168,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BZ.xlsx
+++ b/output/pdf_financials_xlsx/BZ.xlsx
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.048247</v>
       </c>
     </row>
     <row r="71">
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.048247</v>
       </c>
     </row>
     <row r="72">
@@ -4584,7 +4584,7 @@
         <v>0.191868</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.496334</v>
+        <v>0.448087</v>
       </c>
     </row>
     <row r="76">
@@ -4883,10 +4883,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P80" s="3" t="n">
+        <v>0.002107373536076001</v>
       </c>
     </row>
     <row r="81">
@@ -6532,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.004529</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.018325</v>
       </c>
     </row>
     <row r="111">
@@ -8945,7 +8943,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -15453,7 +15455,11 @@
           <t>Accretion expense 9, 11</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18200,7 +18206,11 @@
           <t>Accretion expense 9</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
